--- a/data/pronostici/TOTOMONDIALE2026_PDM.xlsx
+++ b/data/pronostici/TOTOMONDIALE2026_PDM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demagistris\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.castiello\Documents\totomondiale\data\pronostici\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0EC2DD-FFE1-4E4D-B3A2-9CC3775F54D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D64E6D-01E9-4F7E-B97D-2F5C56E3408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REGOLAMENTO" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="268">
   <si>
     <t>REGOLAMENTO</t>
   </si>
@@ -743,9 +743,6 @@
   </si>
   <si>
     <t>Raphina</t>
-  </si>
-  <si>
-    <t>Foden</t>
   </si>
   <si>
     <t>Leao</t>
@@ -1430,6 +1427,42 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1448,6 +1481,66 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1457,101 +1550,41 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1580,45 +1613,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -2193,7 +2190,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2490,254 +2487,280 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.26953125" style="3" customWidth="1"/>
     <col min="2" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="86"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="74"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88" t="s">
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="89"/>
+      <c r="F2" s="77"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79" t="s">
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="80"/>
+      <c r="F3" s="70"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79" t="s">
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="80"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="81"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="83"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79" t="s">
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="80"/>
+      <c r="F7" s="70"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79" t="s">
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="80"/>
+      <c r="F8" s="70"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79" t="s">
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="80"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="81"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="83"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="80"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79" t="s">
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="80"/>
+      <c r="F11" s="70"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79" t="s">
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="80"/>
+      <c r="F12" s="70"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79" t="s">
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="80"/>
+      <c r="F13" s="70"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="83"/>
+      <c r="A14" s="78"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="78" t="s">
+      <c r="A15" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79" t="s">
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="80"/>
+      <c r="F15" s="70"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="80"/>
+      <c r="F16" s="70"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="80"/>
+      <c r="F17" s="70"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79" t="s">
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="80"/>
+      <c r="F18" s="70"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79" t="s">
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="80"/>
+      <c r="F19" s="70"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="69" t="s">
+      <c r="A20" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="70"/>
-      <c r="C20" s="70"/>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="83"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="72"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="74"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="86"/>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1">
-      <c r="A22" s="75"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="77"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
@@ -2747,32 +2770,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A20:F22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2781,7 +2778,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38C885E-27B6-47B7-8A3A-34CBB58C7420}">
   <dimension ref="A1:T82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="5" width="9.1796875" style="2"/>
     <col min="6" max="6" width="7.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -2795,97 +2792,97 @@
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:20">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="61"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="61"/>
-      <c r="Q5" s="61"/>
-      <c r="R5" s="61"/>
-      <c r="S5" s="61"/>
-      <c r="T5" s="61"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="66" t="s">
+      <c r="J7" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="67"/>
-      <c r="Q7" s="68"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -2897,11 +2894,11 @@
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="62" t="s">
+      <c r="C8" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="4" t="s">
         <v>35</v>
       </c>
@@ -2911,16 +2908,16 @@
       <c r="H8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="63" t="s">
+      <c r="J8" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="65"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="32"/>
     </row>
     <row r="9" spans="1:20" ht="18.5">
       <c r="A9" s="15">
@@ -2929,11 +2926,11 @@
       <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="30"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="7">
         <v>1</v>
       </c>
@@ -2941,22 +2938,22 @@
         <v>199</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="J9" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="J9" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64" t="s">
+      <c r="K9" s="31"/>
+      <c r="L9" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="M9" s="64"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="64" t="s">
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="65"/>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="32"/>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="17">
@@ -2965,11 +2962,11 @@
       <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="45"/>
       <c r="F10" s="8" t="s">
         <v>196</v>
       </c>
@@ -2977,22 +2974,22 @@
         <v>200</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="J10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="59"/>
-      <c r="L10" s="40" t="s">
+      <c r="K10" s="37"/>
+      <c r="L10" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40" t="s">
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="39"/>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="17">
@@ -3001,11 +2998,11 @@
       <c r="B11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="45"/>
       <c r="F11" s="8">
         <v>1</v>
       </c>
@@ -3013,22 +3010,22 @@
         <v>201</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="J11" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="J11" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="59"/>
-      <c r="L11" s="40" t="s">
+      <c r="K11" s="37"/>
+      <c r="L11" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40" t="s">
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="39"/>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="15">
@@ -3037,11 +3034,11 @@
       <c r="B12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
       <c r="F12" s="7">
         <v>1</v>
       </c>
@@ -3049,22 +3046,22 @@
         <v>202</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="J12" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="J12" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="40" t="s">
+      <c r="K12" s="37"/>
+      <c r="L12" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40" t="s">
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="39"/>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="15">
@@ -3073,11 +3070,11 @@
       <c r="B13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="7">
         <v>2</v>
       </c>
@@ -3085,22 +3082,22 @@
         <v>203</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="J13" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="J13" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="K13" s="59"/>
-      <c r="L13" s="40" t="s">
+      <c r="K13" s="37"/>
+      <c r="L13" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40" t="s">
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="41"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="39"/>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="17">
@@ -3109,11 +3106,11 @@
       <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="8">
         <v>1</v>
       </c>
@@ -3123,20 +3120,20 @@
       <c r="H14" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="J14" s="57" t="s">
+      <c r="J14" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="59"/>
-      <c r="L14" s="40" t="s">
+      <c r="K14" s="37"/>
+      <c r="L14" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40" t="s">
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="41"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="39"/>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="17">
@@ -3145,11 +3142,11 @@
       <c r="B15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="45"/>
       <c r="F15" s="8">
         <v>2</v>
       </c>
@@ -3159,20 +3156,20 @@
       <c r="H15" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="J15" s="57" t="s">
+      <c r="J15" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="59"/>
-      <c r="L15" s="40" t="s">
+      <c r="K15" s="37"/>
+      <c r="L15" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40" t="s">
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="41"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="39"/>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="17">
@@ -3181,11 +3178,11 @@
       <c r="B16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="45"/>
       <c r="F16" s="8">
         <v>2</v>
       </c>
@@ -3193,22 +3190,22 @@
         <v>205</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="J16" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="40" t="s">
+      <c r="K16" s="37"/>
+      <c r="L16" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40" t="s">
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="39"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="17">
@@ -3217,11 +3214,11 @@
       <c r="B17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="8">
         <v>1</v>
       </c>
@@ -3231,20 +3228,20 @@
       <c r="H17" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="J17" s="57" t="s">
+      <c r="J17" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="40" t="s">
+      <c r="K17" s="37"/>
+      <c r="L17" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40" t="s">
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="41"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="39"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="17">
@@ -3253,11 +3250,11 @@
       <c r="B18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="45"/>
       <c r="F18" s="8" t="s">
         <v>196</v>
       </c>
@@ -3267,20 +3264,20 @@
       <c r="H18" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="J18" s="57" t="s">
+      <c r="J18" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="K18" s="59"/>
-      <c r="L18" s="40" t="s">
+      <c r="K18" s="37"/>
+      <c r="L18" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40" t="s">
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="41"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="39"/>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="15">
@@ -3289,11 +3286,11 @@
       <c r="B19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
       <c r="F19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3301,22 +3298,22 @@
         <v>207</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="J19" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="J19" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="K19" s="59"/>
-      <c r="L19" s="40" t="s">
+      <c r="K19" s="37"/>
+      <c r="L19" s="38" t="s">
         <v>157</v>
       </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40" t="s">
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="39"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="15">
@@ -3325,11 +3322,11 @@
       <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="42"/>
       <c r="F20" s="7">
         <v>1</v>
       </c>
@@ -3337,22 +3334,22 @@
         <v>200</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="J20" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="J20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="59"/>
-      <c r="L20" s="40" t="s">
+      <c r="K20" s="37"/>
+      <c r="L20" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40" t="s">
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="39"/>
     </row>
     <row r="21" spans="1:17" ht="15" thickBot="1">
       <c r="A21" s="15">
@@ -3361,11 +3358,11 @@
       <c r="B21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="42"/>
       <c r="F21" s="7">
         <v>1</v>
       </c>
@@ -3375,20 +3372,20 @@
       <c r="H21" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J21" s="58" t="s">
+      <c r="J21" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="K21" s="60"/>
-      <c r="L21" s="43" t="s">
+      <c r="K21" s="49"/>
+      <c r="L21" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43" t="s">
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="44"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="47"/>
     </row>
     <row r="22" spans="1:17" ht="15" thickBot="1">
       <c r="A22" s="15">
@@ -3397,11 +3394,11 @@
       <c r="B22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="42"/>
       <c r="F22" s="7">
         <v>1</v>
       </c>
@@ -3419,11 +3416,11 @@
       <c r="B23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="8">
         <v>2</v>
       </c>
@@ -3433,13 +3430,13 @@
       <c r="H23" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="L23" s="45" t="s">
+      <c r="L23" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="46"/>
-      <c r="P23" s="47"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="52"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="17">
@@ -3448,11 +3445,11 @@
       <c r="B24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="8" t="s">
         <v>196</v>
       </c>
@@ -3460,15 +3457,15 @@
         <v>207</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="L24" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="41"/>
+        <v>250</v>
+      </c>
+      <c r="L24" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="39"/>
     </row>
     <row r="25" spans="1:17" ht="15" thickBot="1">
       <c r="A25" s="17">
@@ -3477,11 +3474,11 @@
       <c r="B25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
       <c r="F25" s="8">
         <v>1</v>
       </c>
@@ -3491,11 +3488,11 @@
       <c r="H25" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="L25" s="42"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="44"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="47"/>
     </row>
     <row r="26" spans="1:17" ht="15" thickBot="1">
       <c r="A26" s="15">
@@ -3504,11 +3501,11 @@
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="42"/>
       <c r="F26" s="7">
         <v>2</v>
       </c>
@@ -3526,11 +3523,11 @@
       <c r="B27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="42"/>
       <c r="F27" s="7">
         <v>1</v>
       </c>
@@ -3540,13 +3537,13 @@
       <c r="H27" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="L27" s="54" t="s">
+      <c r="L27" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="57"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="15">
@@ -3555,11 +3552,11 @@
       <c r="B28" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="30"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="42"/>
       <c r="F28" s="7">
         <v>1</v>
       </c>
@@ -3567,17 +3564,17 @@
         <v>201</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="L28" s="57" t="s">
+        <v>251</v>
+      </c>
+      <c r="L28" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="40" t="s">
-        <v>236</v>
-      </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
+      <c r="M28" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="39"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="15">
@@ -3586,11 +3583,11 @@
       <c r="B29" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="30"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
       <c r="F29" s="7">
         <v>1</v>
       </c>
@@ -3600,11 +3597,11 @@
       <c r="H29" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="L29" s="57"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="39"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="15">
@@ -3613,11 +3610,11 @@
       <c r="B30" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="30"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
       <c r="F30" s="7" t="s">
         <v>196</v>
       </c>
@@ -3627,15 +3624,15 @@
       <c r="H30" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="L30" s="57" t="s">
+      <c r="L30" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="M30" s="40" t="s">
+      <c r="M30" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="N30" s="40"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="41"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="39"/>
     </row>
     <row r="31" spans="1:17" ht="15" thickBot="1">
       <c r="A31" s="17">
@@ -3644,11 +3641,11 @@
       <c r="B31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="33"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="45"/>
       <c r="F31" s="8" t="s">
         <v>196</v>
       </c>
@@ -3656,13 +3653,13 @@
         <v>204</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="L31" s="58"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="44"/>
+        <v>252</v>
+      </c>
+      <c r="L31" s="48"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="47"/>
     </row>
     <row r="32" spans="1:17" ht="15" thickBot="1">
       <c r="A32" s="17">
@@ -3671,11 +3668,11 @@
       <c r="B32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="45"/>
       <c r="F32" s="8">
         <v>2</v>
       </c>
@@ -3687,21 +3684,21 @@
       </c>
     </row>
     <row r="33" spans="1:16" ht="18.5">
-      <c r="A33" s="51"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="53"/>
-      <c r="L33" s="45" t="s">
+      <c r="A33" s="58"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="60"/>
+      <c r="L33" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="47"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="51"/>
+      <c r="P33" s="52"/>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="17">
@@ -3710,11 +3707,11 @@
       <c r="B34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="32"/>
-      <c r="E34" s="33"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="45"/>
       <c r="F34" s="8" t="s">
         <v>196</v>
       </c>
@@ -3722,15 +3719,15 @@
         <v>201</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="L34" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="L34" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="M34" s="40"/>
-      <c r="N34" s="40"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="39"/>
     </row>
     <row r="35" spans="1:16" ht="15" thickBot="1">
       <c r="A35" s="17">
@@ -3739,11 +3736,11 @@
       <c r="B35" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="33"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="45"/>
       <c r="F35" s="8">
         <v>1</v>
       </c>
@@ -3751,13 +3748,13 @@
         <v>202</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="L35" s="42"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="44"/>
+        <v>249</v>
+      </c>
+      <c r="L35" s="54"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="47"/>
     </row>
     <row r="36" spans="1:16" ht="15" thickBot="1">
       <c r="A36" s="15">
@@ -3766,11 +3763,11 @@
       <c r="B36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="30"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
       <c r="F36" s="7">
         <v>1</v>
       </c>
@@ -3778,7 +3775,7 @@
         <v>201</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18.5">
@@ -3788,11 +3785,11 @@
       <c r="B37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="30"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="42"/>
       <c r="F37" s="7">
         <v>2</v>
       </c>
@@ -3800,15 +3797,15 @@
         <v>205</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="L37" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="L37" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="47"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="51"/>
+      <c r="P37" s="52"/>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="15">
@@ -3817,11 +3814,11 @@
       <c r="B38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="29"/>
-      <c r="E38" s="30"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="42"/>
       <c r="F38" s="7" t="s">
         <v>196</v>
       </c>
@@ -3829,15 +3826,15 @@
         <v>201</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="L38" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="L38" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="M38" s="40"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="40"/>
-      <c r="P38" s="41"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="39"/>
     </row>
     <row r="39" spans="1:16" ht="15" thickBot="1">
       <c r="A39" s="17">
@@ -3846,11 +3843,11 @@
       <c r="B39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="33"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="45"/>
       <c r="F39" s="8">
         <v>2</v>
       </c>
@@ -3858,13 +3855,13 @@
         <v>203</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="L39" s="42"/>
-      <c r="M39" s="43"/>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="44"/>
+        <v>253</v>
+      </c>
+      <c r="L39" s="54"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="47"/>
     </row>
     <row r="40" spans="1:16" ht="15" thickBot="1">
       <c r="A40" s="17">
@@ -3873,11 +3870,11 @@
       <c r="B40" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="32"/>
-      <c r="E40" s="33"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="45"/>
       <c r="F40" s="8">
         <v>1</v>
       </c>
@@ -3895,11 +3892,11 @@
       <c r="B41" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="32"/>
-      <c r="E41" s="33"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="45"/>
       <c r="F41" s="8">
         <v>1</v>
       </c>
@@ -3907,15 +3904,15 @@
         <v>200</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="L41" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="L41" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="46"/>
-      <c r="P41" s="47"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="51"/>
+      <c r="P41" s="52"/>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="17">
@@ -3924,11 +3921,11 @@
       <c r="B42" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="33"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="45"/>
       <c r="F42" s="8" t="s">
         <v>196</v>
       </c>
@@ -3936,15 +3933,15 @@
         <v>199</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="L42" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="L42" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="M42" s="40"/>
-      <c r="N42" s="40"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="41"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="39"/>
     </row>
     <row r="43" spans="1:16" ht="15" thickBot="1">
       <c r="A43" s="17">
@@ -3953,11 +3950,11 @@
       <c r="B43" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C43" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="33"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="45"/>
       <c r="F43" s="8">
         <v>1</v>
       </c>
@@ -3967,11 +3964,11 @@
       <c r="H43" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="L43" s="42"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="44"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="47"/>
     </row>
     <row r="44" spans="1:16" ht="15" thickBot="1">
       <c r="A44" s="15">
@@ -3980,11 +3977,11 @@
       <c r="B44" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="29"/>
-      <c r="E44" s="30"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="42"/>
       <c r="F44" s="7">
         <v>1</v>
       </c>
@@ -3992,7 +3989,7 @@
         <v>202</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18.5">
@@ -4002,11 +3999,11 @@
       <c r="B45" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="29"/>
-      <c r="E45" s="30"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="42"/>
       <c r="F45" s="7">
         <v>2</v>
       </c>
@@ -4014,15 +4011,15 @@
         <v>201</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="L45" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="L45" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="47"/>
+      <c r="M45" s="51"/>
+      <c r="N45" s="51"/>
+      <c r="O45" s="51"/>
+      <c r="P45" s="52"/>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="15">
@@ -4031,11 +4028,11 @@
       <c r="B46" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="29"/>
-      <c r="E46" s="30"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="42"/>
       <c r="F46" s="7">
         <v>1</v>
       </c>
@@ -4045,13 +4042,13 @@
       <c r="H46" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="L46" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="M46" s="40"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="40"/>
-      <c r="P46" s="41"/>
+      <c r="L46" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="39"/>
     </row>
     <row r="47" spans="1:16" ht="15" thickBot="1">
       <c r="A47" s="15">
@@ -4060,11 +4057,11 @@
       <c r="B47" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="30"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="42"/>
       <c r="F47" s="7">
         <v>1</v>
       </c>
@@ -4074,11 +4071,11 @@
       <c r="H47" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="L47" s="42"/>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="43"/>
-      <c r="P47" s="44"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
+      <c r="P47" s="47"/>
     </row>
     <row r="48" spans="1:16" ht="15" thickBot="1">
       <c r="A48" s="17">
@@ -4087,11 +4084,11 @@
       <c r="B48" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="C48" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="32"/>
-      <c r="E48" s="33"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="45"/>
       <c r="F48" s="8">
         <v>1</v>
       </c>
@@ -4099,7 +4096,7 @@
         <v>202</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18.5">
@@ -4109,11 +4106,11 @@
       <c r="B49" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="D49" s="32"/>
-      <c r="E49" s="33"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="45"/>
       <c r="F49" s="8">
         <v>2</v>
       </c>
@@ -4121,15 +4118,15 @@
         <v>203</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="L49" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="L49" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="47"/>
+      <c r="M49" s="51"/>
+      <c r="N49" s="51"/>
+      <c r="O49" s="51"/>
+      <c r="P49" s="52"/>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="17">
@@ -4138,11 +4135,11 @@
       <c r="B50" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="33"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="45"/>
       <c r="F50" s="8">
         <v>1</v>
       </c>
@@ -4152,13 +4149,13 @@
       <c r="H50" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="L50" s="39" t="s">
+      <c r="L50" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="41"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="39"/>
     </row>
     <row r="51" spans="1:16" ht="15" thickBot="1">
       <c r="A51" s="17">
@@ -4167,11 +4164,11 @@
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="32"/>
-      <c r="E51" s="33"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="45"/>
       <c r="F51" s="8">
         <v>1</v>
       </c>
@@ -4181,11 +4178,11 @@
       <c r="H51" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="L51" s="42"/>
-      <c r="M51" s="43"/>
-      <c r="N51" s="43"/>
-      <c r="O51" s="43"/>
-      <c r="P51" s="44"/>
+      <c r="L51" s="54"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="47"/>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="15">
@@ -4194,11 +4191,11 @@
       <c r="B52" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="29"/>
-      <c r="E52" s="30"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="42"/>
       <c r="F52" s="7">
         <v>1</v>
       </c>
@@ -4216,11 +4213,11 @@
       <c r="B53" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="D53" s="29"/>
-      <c r="E53" s="30"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="42"/>
       <c r="F53" s="7">
         <v>2</v>
       </c>
@@ -4228,7 +4225,7 @@
         <v>207</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4238,11 +4235,11 @@
       <c r="B54" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C54" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="29"/>
-      <c r="E54" s="30"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="42"/>
       <c r="F54" s="7">
         <v>1</v>
       </c>
@@ -4260,11 +4257,11 @@
       <c r="B55" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C55" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="29"/>
-      <c r="E55" s="30"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="42"/>
       <c r="F55" s="7">
         <v>1</v>
       </c>
@@ -4282,11 +4279,11 @@
       <c r="B56" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="31" t="s">
+      <c r="C56" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="D56" s="32"/>
-      <c r="E56" s="33"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="45"/>
       <c r="F56" s="8">
         <v>2</v>
       </c>
@@ -4294,7 +4291,7 @@
         <v>205</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4304,11 +4301,11 @@
       <c r="B57" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="33"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="45"/>
       <c r="F57" s="8">
         <v>1</v>
       </c>
@@ -4320,14 +4317,14 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="48"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="50"/>
+      <c r="A58" s="61"/>
+      <c r="B58" s="62"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="62"/>
+      <c r="H58" s="63"/>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="17">
@@ -4336,11 +4333,11 @@
       <c r="B59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="D59" s="32"/>
-      <c r="E59" s="33"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="45"/>
       <c r="F59" s="8">
         <v>1</v>
       </c>
@@ -4348,7 +4345,7 @@
         <v>201</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4358,11 +4355,11 @@
       <c r="B60" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="31" t="s">
+      <c r="C60" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="D60" s="32"/>
-      <c r="E60" s="33"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="45"/>
       <c r="F60" s="8">
         <v>1</v>
       </c>
@@ -4370,7 +4367,7 @@
         <v>207</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4380,11 +4377,11 @@
       <c r="B61" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="C61" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="D61" s="29"/>
-      <c r="E61" s="30"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="42"/>
       <c r="F61" s="7" t="s">
         <v>196</v>
       </c>
@@ -4402,11 +4399,11 @@
       <c r="B62" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="C62" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="29"/>
-      <c r="E62" s="30"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="42"/>
       <c r="F62" s="7">
         <v>1</v>
       </c>
@@ -4424,11 +4421,11 @@
       <c r="B63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="29"/>
-      <c r="E63" s="30"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="42"/>
       <c r="F63" s="7" t="s">
         <v>196</v>
       </c>
@@ -4436,7 +4433,7 @@
         <v>201</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4446,11 +4443,11 @@
       <c r="B64" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="C64" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="D64" s="29"/>
-      <c r="E64" s="30"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="42"/>
       <c r="F64" s="7">
         <v>2</v>
       </c>
@@ -4458,7 +4455,7 @@
         <v>203</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -4468,11 +4465,11 @@
       <c r="B65" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="C65" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D65" s="29"/>
-      <c r="E65" s="30"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="42"/>
       <c r="F65" s="7">
         <v>2</v>
       </c>
@@ -4490,11 +4487,11 @@
       <c r="B66" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="C66" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="D66" s="29"/>
-      <c r="E66" s="30"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="42"/>
       <c r="F66" s="7">
         <v>2</v>
       </c>
@@ -4502,7 +4499,7 @@
         <v>201</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -4512,11 +4509,11 @@
       <c r="B67" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="D67" s="32"/>
-      <c r="E67" s="33"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="45"/>
       <c r="F67" s="8">
         <v>2</v>
       </c>
@@ -4524,7 +4521,7 @@
         <v>205</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -4534,11 +4531,11 @@
       <c r="B68" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="33"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="45"/>
       <c r="F68" s="8">
         <v>1</v>
       </c>
@@ -4546,7 +4543,7 @@
         <v>201</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -4556,11 +4553,11 @@
       <c r="B69" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="32"/>
-      <c r="E69" s="33"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="45"/>
       <c r="F69" s="8" t="s">
         <v>196</v>
       </c>
@@ -4576,11 +4573,11 @@
       <c r="B70" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C70" s="31" t="s">
+      <c r="C70" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="D70" s="32"/>
-      <c r="E70" s="33"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="45"/>
       <c r="F70" s="8">
         <v>2</v>
       </c>
@@ -4588,7 +4585,7 @@
         <v>201</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -4598,11 +4595,11 @@
       <c r="B71" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="31" t="s">
+      <c r="C71" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="32"/>
-      <c r="E71" s="33"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="45"/>
       <c r="F71" s="8">
         <v>2</v>
       </c>
@@ -4620,11 +4617,11 @@
       <c r="B72" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C72" s="31" t="s">
+      <c r="C72" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="33"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="45"/>
       <c r="F72" s="8">
         <v>1</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>199</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -4642,11 +4639,11 @@
       <c r="B73" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D73" s="29"/>
-      <c r="E73" s="30"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="42"/>
       <c r="F73" s="7" t="s">
         <v>196</v>
       </c>
@@ -4664,11 +4661,11 @@
       <c r="B74" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="29"/>
-      <c r="E74" s="30"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="42"/>
       <c r="F74" s="7">
         <v>2</v>
       </c>
@@ -4676,7 +4673,7 @@
         <v>201</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -4686,11 +4683,11 @@
       <c r="B75" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="28" t="s">
+      <c r="C75" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="D75" s="29"/>
-      <c r="E75" s="30"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="42"/>
       <c r="F75" s="7">
         <v>1</v>
       </c>
@@ -4698,7 +4695,7 @@
         <v>202</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -4708,11 +4705,11 @@
       <c r="B76" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C76" s="28" t="s">
+      <c r="C76" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="D76" s="29"/>
-      <c r="E76" s="30"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="42"/>
       <c r="F76" s="7">
         <v>2</v>
       </c>
@@ -4720,7 +4717,7 @@
         <v>203</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -4730,11 +4727,11 @@
       <c r="B77" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C77" s="28" t="s">
+      <c r="C77" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D77" s="29"/>
-      <c r="E77" s="30"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="42"/>
       <c r="F77" s="7">
         <v>2</v>
       </c>
@@ -4742,7 +4739,7 @@
         <v>211</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -4752,11 +4749,11 @@
       <c r="B78" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C78" s="28" t="s">
+      <c r="C78" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="29"/>
-      <c r="E78" s="30"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="42"/>
       <c r="F78" s="7">
         <v>1</v>
       </c>
@@ -4764,7 +4761,7 @@
         <v>200</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -4774,11 +4771,11 @@
       <c r="B79" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="32"/>
-      <c r="E79" s="33"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="45"/>
       <c r="F79" s="8">
         <v>2</v>
       </c>
@@ -4786,7 +4783,7 @@
         <v>204</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -4796,11 +4793,11 @@
       <c r="B80" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="31" t="s">
+      <c r="C80" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="D80" s="32"/>
-      <c r="E80" s="33"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="45"/>
       <c r="F80" s="8" t="s">
         <v>196</v>
       </c>
@@ -4808,7 +4805,7 @@
         <v>207</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -4818,11 +4815,11 @@
       <c r="B81" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C81" s="31" t="s">
+      <c r="C81" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="32"/>
-      <c r="E81" s="33"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="45"/>
       <c r="F81" s="8">
         <v>2</v>
       </c>
@@ -4840,11 +4837,11 @@
       <c r="B82" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C82" s="34" t="s">
+      <c r="C82" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="35"/>
-      <c r="E82" s="36"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="68"/>
       <c r="F82" s="21" t="s">
         <v>196</v>
       </c>
@@ -4852,11 +4849,126 @@
         <v>205</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="139">
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="L42:P43"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="L46:P47"/>
+    <mergeCell ref="L49:P49"/>
+    <mergeCell ref="L50:P51"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="L33:P33"/>
+    <mergeCell ref="L34:P35"/>
+    <mergeCell ref="L37:P37"/>
+    <mergeCell ref="L38:P39"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P25"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="M30:P31"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
     <mergeCell ref="A5:T6"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="J8:Q8"/>
@@ -4881,121 +4993,6 @@
     <mergeCell ref="O9:Q9"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="L24:P25"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M28:P29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="M30:P31"/>
-    <mergeCell ref="L33:P33"/>
-    <mergeCell ref="L34:P35"/>
-    <mergeCell ref="L37:P37"/>
-    <mergeCell ref="L38:P39"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="L42:P43"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="L46:P47"/>
-    <mergeCell ref="L49:P49"/>
-    <mergeCell ref="L50:P51"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -5088,7 +5085,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08492CED-BD82-40E8-8535-9476C55F213E}">
   <dimension ref="A2:A80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
